--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -9892,7 +9892,7 @@
     <t>1498</t>
   </si>
   <si>
-    <t>Accompagnement ergothérapique auprès des proches aidants (proches et professionnels) : apprentissage de techniques d'accompagnement</t>
+    <t>Accompagnement ergothérapique auprès des proches aidants (proches et professionnels) : apprentissage de techniques d’accompagnement en Accompagnement ergothérapique auprès des proches aidants</t>
   </si>
   <si>
     <t>Apprentissage de techniques d’accompagnement ergothérapique qui vise à améliorer la compréhension de l’impact de la pathologie dans le quotidien et à mettre en place des stratégies d’adaptation visant l’amélioration de la qualité de vie et la participation.  Cet accompagnement inclut l’évaluation des compétences, l’orientation professionnelle, la formation, l’adaptation des postes de travail et la coordination avec les acteurs médico-sociaux, afin de favoriser une intégration professionnelle durable et adaptée aux capacités de la personne.Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>

--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -9892,7 +9892,7 @@
     <t>1498</t>
   </si>
   <si>
-    <t>Accompagnement ergothérapique auprès des proches aidants (proches et professionnels) : apprentissage de techniques d’accompagnement en Accompagnement ergothérapique auprès des proches aidants</t>
+    <t>Accompagnement ergothérapique auprès des proches aidants (proches et professionnels) : apprentissage de techniques d'accompagnement</t>
   </si>
   <si>
     <t>Apprentissage de techniques d’accompagnement ergothérapique qui vise à améliorer la compréhension de l’impact de la pathologie dans le quotidien et à mettre en place des stratégies d’adaptation visant l’amélioration de la qualité de vie et la participation.  Cet accompagnement inclut l’évaluation des compétences, l’orientation professionnelle, la formation, l’adaptation des postes de travail et la coordination avec les acteurs médico-sociaux, afin de favoriser une intégration professionnelle durable et adaptée aux capacités de la personne.Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>

--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -10063,7 +10063,7 @@
     <t>Participation au dispositif HandiGynéco</t>
   </si>
   <si>
-    <t>Démarche qui permet à des sages-femmes libérales, volontaires et formées au handicap, d’intervenir directement dans les établissements médico-sociaux (FAM, MAS, EAM),  auprès des résidentes pour réduire les obstacles à l’accès aux soins gynécologiques des femmes en situation de handicap et d'assurer des consultations gynécologiques adaptées, des ateliers de vie affective et sexuelle, ainsi que des actions de prévention des violences faites aux femmes (objective de faciliter l’accès aux soins et à l’information)</t>
+    <t>Démarche qui permet à des sages-femmes libérales, volontaires et formées au handicap, d’intervenir directement dans les établissements médico-sociaux (FAM, MAS, EAM),  auprès des résidentes pour réduire les obstacles à l’accès aux soins gynécologiques des femmes en situation de handicap et d'assurer des consultations gynécologiques adaptées, des ateliers de vie affective et sexuelle, ainsi que des actions de prévention des violences faites aux femmes (objectif de faciliter l’accès aux soins et à l’information)</t>
   </si>
   <si>
     <t>1519</t>
